--- a/MainTop/18.09.2026 3гор/поставка/Петербург_print_sorted.xlsx
+++ b/MainTop/18.09.2026 3гор/поставка/Петербург_print_sorted.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L2" s="1" t="n">
@@ -590,7 +590,7 @@
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
@@ -702,7 +702,7 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
@@ -758,7 +758,7 @@
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
@@ -814,7 +814,7 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L7" s="1" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L8" s="1" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L9" s="1" t="n">
@@ -982,7 +982,7 @@
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L10" s="1" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L11" s="1" t="n">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L12" s="1" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L13" s="1" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L14" s="1" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L15" s="1" t="n">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L16" s="1" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L17" s="1" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L18" s="1" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L19" s="1" t="n">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L20" s="1" t="n">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L21" s="1" t="n">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L22" s="1" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L23" s="1" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L24" s="1" t="n">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L25" s="1" t="n">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L26" s="1" t="n">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L27" s="1" t="n">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L28" s="1" t="n">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L29" s="1" t="n">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L30" s="1" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L31" s="1" t="n">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L32" s="1" t="n">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="K33" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L33" s="1" t="n">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L34" s="1" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="K35" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L35" s="1" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L36" s="1" t="n">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K37" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L37" s="1" t="n">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K38" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L38" s="1" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="K39" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L39" s="1" t="n">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="K40" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L40" s="1" t="n">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="K41" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L41" s="1" t="n">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="K42" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L42" s="1" t="n">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="K43" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L43" s="1" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="K44" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L44" s="1" t="n">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="K45" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L45" s="1" t="n">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="K46" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L46" s="1" t="n">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K47" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L47" s="1" t="n">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="K48" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L48" s="1" t="n">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="K49" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L49" s="1" t="n">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="K50" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L50" s="1" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K51" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L51" s="1" t="n">
